--- a/week-01/assignments/Ex5B_RestrauntantSurvey1.xlsx
+++ b/week-01/assignments/Ex5B_RestrauntantSurvey1.xlsx
@@ -8,24 +8,39 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeremiahgoode\AppData\Local\Programs\Git\DataAnalytics\week-01\assignments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ADAE11CF-65B2-4573-A77F-78978A9CB5B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47265EF5-9394-447D-AE67-42C30F1DA1FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="99" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="32">
   <si>
     <t>ID</t>
   </si>
@@ -39,12 +54,6 @@
     <t>Email</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Last modified time</t>
-  </si>
-  <si>
     <t>How Did You Enjoy Your Visit </t>
   </si>
   <si>
@@ -115,6 +124,18 @@
   </si>
   <si>
     <t>everything was good except for the wait time. Had to wait 3 hours longer than expected</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Count of Email</t>
   </si>
 </sst>
 </file>
@@ -124,7 +145,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,14 +174,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="20">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -181,6 +220,21 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -210,22 +264,1917 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Ex5B_RestrauntantSurvey1.xlsx]Sheet2!PivotTable20</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="25000"/>
+                  <a:lumOff val="75000"/>
+                </a:sysClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                <a:prstGeom prst="wedgeRectCallout">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+              </c15:spPr>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="25000"/>
+                  <a:lumOff val="75000"/>
+                </a:sysClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                <a:prstGeom prst="wedgeRectCallout">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+              </c15:spPr>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent3"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="25000"/>
+                  <a:lumOff val="75000"/>
+                </a:sysClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                <a:prstGeom prst="wedgeRectCallout">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+              </c15:spPr>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent4"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="25000"/>
+                  <a:lumOff val="75000"/>
+                </a:sysClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                <a:prstGeom prst="wedgeRectCallout">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+              </c15:spPr>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-7E4E-4526-834E-06585EA653DB}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000004-7E4E-4526-834E-06585EA653DB}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-7E4E-4526-834E-06585EA653DB}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000006-7E4E-4526-834E-06585EA653DB}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:sysClr val="window" lastClr="FFFFFF"/>
+                </a:solidFill>
+                <a:ln>
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="25000"/>
+                      <a:lumOff val="75000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <a:prstGeom prst="wedgeRectCallout">
+                      <a:avLst/>
+                    </a:prstGeom>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                  </c15:spPr>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-7E4E-4526-834E-06585EA653DB}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:sysClr val="window" lastClr="FFFFFF"/>
+                </a:solidFill>
+                <a:ln>
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="25000"/>
+                      <a:lumOff val="75000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <a:prstGeom prst="wedgeRectCallout">
+                      <a:avLst/>
+                    </a:prstGeom>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                  </c15:spPr>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-7E4E-4526-834E-06585EA653DB}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:sysClr val="window" lastClr="FFFFFF"/>
+                </a:solidFill>
+                <a:ln>
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="25000"/>
+                      <a:lumOff val="75000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <a:prstGeom prst="wedgeRectCallout">
+                      <a:avLst/>
+                    </a:prstGeom>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                  </c15:spPr>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-7E4E-4526-834E-06585EA653DB}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:sysClr val="window" lastClr="FFFFFF"/>
+                </a:solidFill>
+                <a:ln>
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="25000"/>
+                      <a:lumOff val="75000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <a:prstGeom prst="wedgeRectCallout">
+                      <a:avLst/>
+                    </a:prstGeom>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                  </c15:spPr>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-7E4E-4526-834E-06585EA653DB}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Alright</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Awesome </c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Good</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Okay</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$B$2:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7E4E-4526-834E-06585EA653DB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="0"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94C2C174-BC05-E61E-503B-FC3871F47919}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="jeremiah goode" refreshedDate="46122.716531597223" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="6" xr:uid="{DD491B80-EA0E-49B2-8CE2-8D0F60761895}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table1[[Email]:[Did You Try Our New Loaded Cheese Fries]]"/>
+  </cacheSource>
+  <cacheFields count="8">
+    <cacheField name="Email" numFmtId="0">
+      <sharedItems count="1">
+        <s v="anonymous"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Name" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1" count="1">
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Last modified time" numFmtId="164">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="How Did You Enjoy Your Visit " numFmtId="0">
+      <sharedItems count="4">
+        <s v="Good"/>
+        <s v="Alright"/>
+        <s v="Okay"/>
+        <s v="Awesome "/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="How Often Do You Visit?" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Would You Recommend A Friend?" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="How Did You Hear About Us??" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Did You Try Our New Loaded Cheese Fries" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="6">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <x v="0"/>
+    <s v="Weekly"/>
+    <s v="Yes"/>
+    <s v="Tiktok"/>
+    <s v="Yes"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <x v="0"/>
+    <s v="Monthly"/>
+    <s v="Yes"/>
+    <s v="Tiktok"/>
+    <s v="No"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <x v="1"/>
+    <s v="Seasonal"/>
+    <s v="No"/>
+    <s v="Tiktok"/>
+    <s v="No"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <x v="2"/>
+    <s v="Monthly"/>
+    <s v="Maybe"/>
+    <s v="Tiktok"/>
+    <s v="No"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <x v="3"/>
+    <s v="Monthly"/>
+    <s v="Yes"/>
+    <s v="I live nearby"/>
+    <s v="No"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <x v="3"/>
+    <s v="Monthly"/>
+    <s v="Yes"/>
+    <s v="Tiktok"/>
+    <s v=" "/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5B268E1-66A3-4A0E-BC20-36E25B89B393}" name="PivotTable20" cacheId="99" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+  <location ref="A1:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField dataField="1" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Email" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="5">
+    <chartFormat chart="0" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:L7" totalsRowShown="0">
-  <autoFilter ref="A1:L7" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Completion time" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Last modified time" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="How Did You Enjoy Your Visit " dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="How Often Do You Visit?" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Would You Recommend A Friend?" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="How Did You Hear About Us??" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Did You Try Our New Loaded Cheese Fries" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="What Are Some Things That We Did Well or Need to Improve On for Your Next Visit" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:J8" totalsRowCount="1">
+  <autoFilter ref="A1:J7" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="19" totalsRowDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time" dataDxfId="18" totalsRowDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Completion time" dataDxfId="17" totalsRowDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="16" totalsRowDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="How Did You Enjoy Your Visit " totalsRowFunction="custom" dataDxfId="15" totalsRowDxfId="7">
+      <totalsRowFormula>COUNTIF(Table1[How Did You Enjoy Your Visit ],"Good")</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="How Often Do You Visit?" totalsRowFunction="custom" dataDxfId="14" totalsRowDxfId="6">
+      <totalsRowFormula>COUNTIF(Table1[How Often Do You Visit?],"Monthly")</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Would You Recommend A Friend?" totalsRowFunction="custom" dataDxfId="13" totalsRowDxfId="5">
+      <totalsRowFormula>COUNTIF(Table1[Would You Recommend A Friend?],"Yes")</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="How Did You Hear About Us??" totalsRowFunction="custom" dataDxfId="12" totalsRowDxfId="4">
+      <totalsRowFormula>COUNTIF(Table1[How Did You Hear About Us??],"Tiktok")</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Did You Try Our New Loaded Cheese Fries" totalsRowFunction="custom" dataDxfId="1" totalsRowDxfId="3">
+      <totalsRowFormula>COUNTIF(Table1[Did You Try Our New Loaded Cheese Fries],"No")</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="What Are Some Things That We Did Well or Need to Improve On for Your Next Visit" dataDxfId="0" totalsRowDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -527,14 +2476,86 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AF4A6A1-8FB1-4FC5-8E9E-C097C1DC8395}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="12" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
+      <c r="A1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="3">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.109375" customWidth="1"/>
+    <col min="6" max="6" width="19.21875" customWidth="1"/>
+    <col min="7" max="7" width="29.21875" customWidth="1"/>
+    <col min="8" max="8" width="28.5546875" customWidth="1"/>
+    <col min="9" max="9" width="32.21875" customWidth="1"/>
+    <col min="10" max="10" width="39.44140625" customWidth="1"/>
+    <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="79" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="28.8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -547,32 +2568,26 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="28.8">
       <c r="A2">
         <v>1</v>
       </c>
@@ -583,9 +2598,14 @@
         <v>46121.598530092597</v>
       </c>
       <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1"/>
       <c r="G2" t="s">
         <v>13</v>
       </c>
@@ -593,19 +2613,13 @@
         <v>14</v>
       </c>
       <c r="I2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="J2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" t="s">
-        <v>17</v>
-      </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>2</v>
       </c>
@@ -616,26 +2630,26 @@
         <v>46121.945127314801</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
       <c r="G3" t="s">
         <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3" t="s">
-        <v>19</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="28.8">
       <c r="A4">
         <v>3</v>
       </c>
@@ -646,29 +2660,28 @@
         <v>46122.414548611101</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
       <c r="G4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L4" t="s">
-        <v>22</v>
-      </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="28.8">
       <c r="A5">
         <v>4</v>
       </c>
@@ -679,29 +2692,28 @@
         <v>46122.465659722198</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
       <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5" t="s">
-        <v>19</v>
-      </c>
-      <c r="L5" t="s">
-        <v>25</v>
-      </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>5</v>
       </c>
@@ -712,29 +2724,28 @@
         <v>46122.496296296304</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
       <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" t="s">
-        <v>28</v>
-      </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="28.8">
       <c r="A7">
         <v>6</v>
       </c>
@@ -745,27 +2756,53 @@
         <v>46122.573634259301</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" t="s">
-        <v>19</v>
-      </c>
-      <c r="L7" t="s">
-        <v>29</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="3"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3">
+        <f>COUNTIF(Table1[How Did You Enjoy Your Visit ],"Good")</f>
+        <v>2</v>
+      </c>
+      <c r="F8" s="3">
+        <f>COUNTIF(Table1[How Often Do You Visit?],"Monthly")</f>
+        <v>4</v>
+      </c>
+      <c r="G8" s="3">
+        <f>COUNTIF(Table1[Would You Recommend A Friend?],"Yes")</f>
+        <v>4</v>
+      </c>
+      <c r="H8" s="3">
+        <f>COUNTIF(Table1[How Did You Hear About Us??],"Tiktok")</f>
+        <v>5</v>
+      </c>
+      <c r="I8" s="3">
+        <f>COUNTIF(Table1[Did You Try Our New Loaded Cheese Fries],"No")</f>
+        <v>4</v>
+      </c>
+      <c r="J8" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
